--- a/REQ_CASH_Form_Template.xlsx
+++ b/REQ_CASH_Form_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Shui On\Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE673470-73C0-4F63-BE25-D4711AC3558F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9575D5F9-A93F-4ACB-9968-046859982DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D27A51AB-3ECD-4D66-BEDD-4E344D037134}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Requisition Form - CASH/CHEQUE PAYMENT</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -68,12 +68,6 @@
   <si>
     <t>Approved by:</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chris CHAN</t>
-  </si>
-  <si>
-    <t>Dominic AU YEUNG</t>
   </si>
   <si>
     <t>#</t>
@@ -653,7 +647,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.90625" customWidth="1"/>
@@ -675,7 +669,7 @@
     </row>
     <row r="3" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>1</v>
@@ -684,7 +678,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>3</v>
@@ -752,9 +746,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C14" s="9"/>
@@ -775,11 +767,6 @@
         <v>7</v>
       </c>
       <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="F18" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -801,16 +788,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1fd0e686-1731-4998-98c5-1c2ea6b88a21">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D213D087CB9854680D1164CCEB123C5" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="332df79206042e1bcd4e1a528c3fc925">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1fd0e686-1731-4998-98c5-1c2ea6b88a21" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="256be6c283d591dcc756e3d269a16f97" ns2:_="">
     <xsd:import namespace="1fd0e686-1731-4998-98c5-1c2ea6b88a21"/>
@@ -988,6 +965,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1fd0e686-1731-4998-98c5-1c2ea6b88a21">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1FB5C22-434C-476B-AD5F-3CCAE2D539F5}">
   <ds:schemaRefs>
@@ -997,16 +984,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A42D8EB-41A8-4D50-97FD-B85E0E281A6D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1fd0e686-1731-4998-98c5-1c2ea6b88a21"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D195B25-3EC9-4EE5-A19E-2C5277259564}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1022,4 +999,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A42D8EB-41A8-4D50-97FD-B85E0E281A6D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1fd0e686-1731-4998-98c5-1c2ea6b88a21"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>